--- a/00 Raw data/SDG/Publications_by_SDG_-_National_Pingtung_University_of_Science_and_Technology.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_National_Pingtung_University_of_Science_and_Technology.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -212,10 +212,10 @@
         <v>17.0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>170.0</v>
+        <v>174.0</v>
       </c>
     </row>
     <row r="14">
@@ -225,13 +225,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>197.0</v>
+        <v>201.0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D14" t="n">
-        <v>2424.0</v>
+        <v>2577.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>514.0</v>
+        <v>547.0</v>
       </c>
       <c r="C15" t="n">
         <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>7105.0</v>
+        <v>8262.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>93.0</v>
+        <v>99.0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="D16" t="n">
-        <v>994.0</v>
+        <v>1058.0</v>
       </c>
     </row>
     <row r="17">
@@ -276,10 +276,10 @@
         <v>17.0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="D17" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="18">
@@ -289,13 +289,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>109.0</v>
+        <v>122.0</v>
       </c>
       <c r="C18" t="n">
         <v>0.66</v>
       </c>
       <c r="D18" t="n">
-        <v>1248.0</v>
+        <v>1566.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>162.0</v>
+        <v>174.0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="D19" t="n">
-        <v>1806.0</v>
+        <v>2145.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>136.0</v>
+        <v>147.0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="D20" t="n">
-        <v>1667.0</v>
+        <v>1998.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>239.0</v>
+        <v>249.0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="D21" t="n">
-        <v>3290.0</v>
+        <v>3905.0</v>
       </c>
     </row>
     <row r="22">
@@ -359,7 +359,7 @@
         <v>0.51</v>
       </c>
       <c r="D22" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="D23" t="n">
-        <v>1211.0</v>
+        <v>1300.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>210.0</v>
+        <v>222.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="D24" t="n">
-        <v>3762.0</v>
+        <v>4078.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>132.0</v>
+        <v>139.0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="D25" t="n">
-        <v>1515.0</v>
+        <v>1736.0</v>
       </c>
     </row>
     <row r="26">
@@ -417,13 +417,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>205.0</v>
+        <v>218.0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>3732.0</v>
+        <v>4566.0</v>
       </c>
     </row>
     <row r="27">
@@ -433,13 +433,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>129.0</v>
+        <v>134.0</v>
       </c>
       <c r="C27" t="n">
         <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>1125.0</v>
+        <v>1214.0</v>
       </c>
     </row>
     <row r="28">
@@ -452,10 +452,10 @@
         <v>23.0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="D28" t="n">
-        <v>138.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1533.0</v>
+        <v>1634.0</v>
       </c>
       <c r="C29" t="n">
         <v>1.01</v>
       </c>
       <c r="D29" t="n">
-        <v>20601.0</v>
+        <v>24209.0</v>
       </c>
     </row>
     <row r="30">
